--- a/backend/sample_departments.xlsx
+++ b/backend/sample_departments.xlsx
@@ -437,34 +437,34 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>ECE</v>
+        <v>CE</v>
       </c>
       <c r="B5" t="str">
-        <v>Electronics and Communication Engineering</v>
+        <v>Civil Engineering</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>CA</v>
+        <v>EE</v>
       </c>
       <c r="B6" t="str">
-        <v>Computer Applications</v>
+        <v>Electrical and Electronics Engineering</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>EE</v>
+        <v>AI</v>
       </c>
       <c r="B7" t="str">
-        <v>Electrical and Electronics Engineering</v>
+        <v>Artificial Intelligence and Data Science</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>CE</v>
+        <v>CA</v>
       </c>
       <c r="B8" t="str">
-        <v>Civil Engineering</v>
+        <v>Computer Applications</v>
       </c>
     </row>
   </sheetData>
